--- a/bakup/customers/morteza shamsi.xlsx
+++ b/bakup/customers/morteza shamsi.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="152">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -397,6 +397,84 @@
   </si>
   <si>
     <t>1405/06/04</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سیگار   </t>
+  </si>
+  <si>
+    <t>1405/06/10</t>
+  </si>
+  <si>
+    <t>سیگار</t>
+  </si>
+  <si>
+    <t>1405/06/11</t>
+  </si>
+  <si>
+    <t>سیگار تخمه شکلات</t>
+  </si>
+  <si>
+    <t>1405/06/13</t>
+  </si>
+  <si>
+    <t>1405/06/17</t>
+  </si>
+  <si>
+    <t>سیگار ابمیوه</t>
+  </si>
+  <si>
+    <t>1405/06/16</t>
+  </si>
+  <si>
+    <t>1405/06/19</t>
+  </si>
+  <si>
+    <t>1405/06/20</t>
+  </si>
+  <si>
+    <t>1405/06/23</t>
+  </si>
+  <si>
+    <t>سیگلر قهوه</t>
+  </si>
+  <si>
+    <t>1405/07/01</t>
+  </si>
+  <si>
+    <t>1405/07/09</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>قهوه بستنی</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>سیگار تخمه ژاپنی</t>
+  </si>
+  <si>
+    <t>1405/07/15</t>
+  </si>
+  <si>
+    <t>قهوه سیگار تیغ</t>
+  </si>
+  <si>
+    <t>1405/07/16</t>
+  </si>
+  <si>
+    <t>1405/07/19</t>
+  </si>
+  <si>
+    <t>1405/07/21</t>
+  </si>
+  <si>
+    <t>سیگار قهوه شکلات</t>
   </si>
 </sst>
 </file>
@@ -906,7 +984,7 @@
       </c>
       <c r="H2" s="8">
         <f>C115</f>
-        <v>1500000</v>
+        <v>2115000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2208,177 +2286,279 @@
     <row r="95" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <f t="shared" ref="A95:A111" si="4" xml:space="preserve"> A94 +B95-C95</f>
-        <v>1500000</v>
-      </c>
-      <c r="B95" s="7"/>
+        <v>1760000</v>
+      </c>
+      <c r="B95" s="7">
+        <v>260000</v>
+      </c>
       <c r="C95" s="7"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
+      <c r="D95" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B96" s="7"/>
+        <v>1900000</v>
+      </c>
+      <c r="B96" s="7">
+        <v>140000</v>
+      </c>
       <c r="C96" s="7"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
+      <c r="D96" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="97" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B97" s="7"/>
+        <v>2820000</v>
+      </c>
+      <c r="B97" s="7">
+        <v>920000</v>
+      </c>
       <c r="C97" s="7"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
+      <c r="D97" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="98" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B98" s="7"/>
+        <v>3260000</v>
+      </c>
+      <c r="B98" s="7">
+        <v>440000</v>
+      </c>
       <c r="C98" s="7"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
+      <c r="D98" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="99" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B99" s="7"/>
+        <v>3460000</v>
+      </c>
+      <c r="B99" s="7">
+        <v>200000</v>
+      </c>
       <c r="C99" s="7"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
+      <c r="D99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="100" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B100" s="7"/>
+        <v>3730000</v>
+      </c>
+      <c r="B100" s="7">
+        <v>270000</v>
+      </c>
       <c r="C100" s="7"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
+      <c r="D100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="101" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B101" s="7"/>
+        <v>4010000</v>
+      </c>
+      <c r="B101" s="7">
+        <v>280000</v>
+      </c>
       <c r="C101" s="7"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
+      <c r="D101" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="102" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B102" s="7"/>
+        <v>4490000</v>
+      </c>
+      <c r="B102" s="7">
+        <v>480000</v>
+      </c>
       <c r="C102" s="7"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
+      <c r="D102" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="103" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B103" s="7"/>
+        <v>4790000</v>
+      </c>
+      <c r="B103" s="7">
+        <v>300000</v>
+      </c>
       <c r="C103" s="7"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
+      <c r="D103" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="104" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="B104" s="7"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
+      <c r="C104" s="7">
+        <v>4790000</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="105" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B105" s="7"/>
+        <v>230000</v>
+      </c>
+      <c r="B105" s="7">
+        <v>230000</v>
+      </c>
       <c r="C105" s="7"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
+      <c r="D105" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="106" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B106" s="7"/>
+        <v>580000</v>
+      </c>
+      <c r="B106" s="7">
+        <v>350000</v>
+      </c>
       <c r="C106" s="7"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
+      <c r="D106" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="107" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B107" s="7"/>
+        <v>952000</v>
+      </c>
+      <c r="B107" s="7">
+        <v>372000</v>
+      </c>
       <c r="C107" s="7"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
+      <c r="D107" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="108" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B108" s="7"/>
+        <v>1342000</v>
+      </c>
+      <c r="B108" s="7">
+        <v>390000</v>
+      </c>
       <c r="C108" s="7"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
+      <c r="D108" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="109" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B109" s="7"/>
+        <v>1532000</v>
+      </c>
+      <c r="B109" s="7">
+        <v>190000</v>
+      </c>
       <c r="C109" s="7"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
+      <c r="D109" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="110" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B110" s="7"/>
+        <v>1722000</v>
+      </c>
+      <c r="B110" s="7">
+        <v>190000</v>
+      </c>
       <c r="C110" s="7"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
+      <c r="D110" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="111" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <f t="shared" si="4"/>
-        <v>1500000</v>
-      </c>
-      <c r="B111" s="7"/>
+        <v>2115000</v>
+      </c>
+      <c r="B111" s="7">
+        <v>393000</v>
+      </c>
       <c r="C111" s="7"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
+      <c r="D111" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="112" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <f xml:space="preserve"> A111 +B112-C112</f>
-        <v>1500000</v>
+        <v>2115000</v>
       </c>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
@@ -2388,18 +2568,18 @@
     <row r="113" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B113" s="8">
         <f>SUM(B93:B112)+B87</f>
-        <v>14585000</v>
+        <v>19990000</v>
       </c>
       <c r="C113" s="8">
         <f>SUM(C93:C112)+C87</f>
-        <v>12752000</v>
+        <v>17542000</v>
       </c>
     </row>
     <row r="114" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" spans="2:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C115" s="13">
         <f>A112</f>
-        <v>1500000</v>
+        <v>2115000</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>61</v>
